--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133925272</v>
       </c>
       <c r="B2" t="n">
-        <v>99057</v>
+        <v>99085</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133925272</v>
       </c>
       <c r="B2" t="n">
-        <v>99085</v>
+        <v>99095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,218 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>134232494</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99095</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gullblanka, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>499476</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6622065</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134232497</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80423</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gullblanka, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>499572</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6622131</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133925272</v>
       </c>
       <c r="B2" t="n">
-        <v>99095</v>
+        <v>99097</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>134232494</v>
       </c>
       <c r="B3" t="n">
-        <v>99095</v>
+        <v>99097</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>134232497</v>
       </c>
       <c r="B4" t="n">
-        <v>80423</v>
+        <v>80424</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134232497</v>
+        <v>134232494</v>
       </c>
       <c r="B3" t="n">
-        <v>80424</v>
+        <v>99098</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499572</v>
+        <v>499476</v>
       </c>
       <c r="R3" t="n">
-        <v>6622131</v>
+        <v>6622065</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134232494</v>
+        <v>134232497</v>
       </c>
       <c r="B4" t="n">
-        <v>99098</v>
+        <v>80424</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>229497</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499476</v>
+        <v>499572</v>
       </c>
       <c r="R4" t="n">
-        <v>6622065</v>
+        <v>6622131</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,12 +966,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133925272</v>
       </c>
       <c r="B2" t="n">
-        <v>99098</v>
+        <v>99105</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>134232494</v>
       </c>
       <c r="B3" t="n">
-        <v>99098</v>
+        <v>99105</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>134232497</v>
       </c>
       <c r="B4" t="n">
-        <v>80424</v>
+        <v>80431</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133925272</v>
+        <v>134232496</v>
       </c>
       <c r="B2" t="n">
-        <v>99105</v>
+        <v>58136</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499669</v>
+        <v>499676</v>
       </c>
       <c r="R2" t="n">
-        <v>6622001</v>
+        <v>6622345</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -791,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134232494</v>
+        <v>133925272</v>
       </c>
       <c r="B3" t="n">
-        <v>99105</v>
+        <v>99112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,13 +820,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499476</v>
+        <v>499669</v>
       </c>
       <c r="R3" t="n">
-        <v>6622065</v>
+        <v>6622001</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,9 +853,19 @@
           <t>2026-05-26</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134232497</v>
+        <v>134232494</v>
       </c>
       <c r="B4" t="n">
-        <v>80431</v>
+        <v>99112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499572</v>
+        <v>499476</v>
       </c>
       <c r="R4" t="n">
-        <v>6622131</v>
+        <v>6622065</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,12 +966,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1000,6 +1000,112 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134232497</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gullblanka, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>499572</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6622131</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -710,7 +710,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -718,6 +718,8 @@
           <t>med kapsel</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Södra Hagen, Södra Hagen, Vstm</t>
@@ -774,7 +776,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Fjolårskapslar.</t>
+          <t>Fjolårskapslar. Anna Hammars fynd.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,6 +785,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -2731,7 +2734,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3985,7 +3988,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -909,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135060672</v>
+        <v>135143988</v>
       </c>
       <c r="B19" t="n">
-        <v>4776</v>
+        <v>57162</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2640,39 +2640,50 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499518</v>
+        <v>499426</v>
       </c>
       <c r="R19" t="n">
-        <v>6621482</v>
+        <v>6621880</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2699,22 +2710,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Uppflog tupp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2734,17 +2750,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135060532</v>
+        <v>135060672</v>
       </c>
       <c r="B20" t="n">
-        <v>5181</v>
+        <v>4776</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,21 +2768,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2781,10 +2797,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499516</v>
+        <v>499518</v>
       </c>
       <c r="R20" t="n">
-        <v>6621486</v>
+        <v>6621482</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2816,7 +2832,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2826,7 +2842,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2853,52 +2869,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134232496</v>
+        <v>135060532</v>
       </c>
       <c r="B21" t="n">
-        <v>58136</v>
+        <v>5181</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499676</v>
+        <v>499516</v>
       </c>
       <c r="R21" t="n">
-        <v>6622345</v>
+        <v>6621486</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2922,17 +2939,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2947,19 +2969,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135061152</v>
+        <v>134232496</v>
       </c>
       <c r="B22" t="n">
         <v>58136</v>
@@ -2992,24 +3014,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499523</v>
+        <v>499676</v>
       </c>
       <c r="R22" t="n">
-        <v>6621614</v>
+        <v>6622345</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3033,22 +3050,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3063,19 +3075,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135063205</v>
+        <v>135061152</v>
       </c>
       <c r="B23" t="n">
         <v>58136</v>
@@ -3110,19 +3122,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499625</v>
+        <v>499523</v>
       </c>
       <c r="R23" t="n">
-        <v>6622247</v>
+        <v>6621614</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3154,7 +3166,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3164,7 +3176,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3191,7 +3203,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135064184</v>
+        <v>135063205</v>
       </c>
       <c r="B24" t="n">
         <v>58136</v>
@@ -3219,22 +3231,26 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499579</v>
+        <v>499625</v>
       </c>
       <c r="R24" t="n">
-        <v>6622252</v>
+        <v>6622247</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3266,7 +3282,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3276,7 +3292,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3303,39 +3319,35 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135059398</v>
+        <v>135064184</v>
       </c>
       <c r="B25" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
@@ -3343,14 +3355,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499378</v>
+        <v>499579</v>
       </c>
       <c r="R25" t="n">
-        <v>6621540</v>
+        <v>6622251</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3382,7 +3394,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3392,7 +3404,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3419,7 +3431,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135063052</v>
+        <v>135059398</v>
       </c>
       <c r="B26" t="n">
         <v>58131</v>
@@ -3449,7 +3461,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3459,14 +3471,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499604</v>
+        <v>499378</v>
       </c>
       <c r="R26" t="n">
-        <v>6622206</v>
+        <v>6621540</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3498,7 +3510,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3508,7 +3520,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3535,7 +3547,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135063221</v>
+        <v>135063052</v>
       </c>
       <c r="B27" t="n">
         <v>58131</v>
@@ -3575,14 +3587,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499629</v>
+        <v>499604</v>
       </c>
       <c r="R27" t="n">
-        <v>6622247</v>
+        <v>6622206</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3614,7 +3626,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3624,7 +3636,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3651,7 +3663,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135063830</v>
+        <v>135063221</v>
       </c>
       <c r="B28" t="n">
         <v>58131</v>
@@ -3695,10 +3707,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499665</v>
+        <v>499629</v>
       </c>
       <c r="R28" t="n">
-        <v>6622296</v>
+        <v>6622247</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3730,7 +3742,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3740,7 +3752,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3767,7 +3779,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135064196</v>
+        <v>135063830</v>
       </c>
       <c r="B29" t="n">
         <v>58131</v>
@@ -3807,14 +3819,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499579</v>
+        <v>499665</v>
       </c>
       <c r="R29" t="n">
-        <v>6622252</v>
+        <v>6622296</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3846,7 +3858,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3856,7 +3868,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3883,10 +3895,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135060640</v>
+        <v>135064196</v>
       </c>
       <c r="B30" t="n">
-        <v>5201</v>
+        <v>58131</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3894,16 +3906,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>105930</v>
+        <v>103023</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3911,22 +3923,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499509</v>
+        <v>499579</v>
       </c>
       <c r="R30" t="n">
-        <v>6621492</v>
+        <v>6622251</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3958,7 +3974,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3968,7 +3984,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3988,17 +4004,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135059764</v>
+        <v>135060640</v>
       </c>
       <c r="B31" t="n">
-        <v>8449</v>
+        <v>5201</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4006,21 +4022,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4035,10 +4051,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499467</v>
+        <v>499509</v>
       </c>
       <c r="R31" t="n">
-        <v>6621437</v>
+        <v>6621492</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4070,7 +4086,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4080,7 +4096,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4107,38 +4123,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135059416</v>
+        <v>135059764</v>
       </c>
       <c r="B32" t="n">
-        <v>56706</v>
+        <v>8449</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>206046</v>
+        <v>106554</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4147,10 +4163,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499365</v>
+        <v>499467</v>
       </c>
       <c r="R32" t="n">
-        <v>6621528</v>
+        <v>6621437</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4182,7 +4198,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4192,7 +4208,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4219,7 +4235,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135062618</v>
+        <v>135059416</v>
       </c>
       <c r="B33" t="n">
         <v>56706</v>
@@ -4255,14 +4271,14 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499537</v>
+        <v>499365</v>
       </c>
       <c r="R33" t="n">
-        <v>6622009</v>
+        <v>6621528</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4294,7 +4310,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4304,7 +4320,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4331,52 +4347,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133925272</v>
+        <v>135062618</v>
       </c>
       <c r="B34" t="n">
-        <v>99112</v>
+        <v>56706</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219790</v>
+        <v>206046</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499669</v>
+        <v>499537</v>
       </c>
       <c r="R34" t="n">
-        <v>6622001</v>
+        <v>6622009</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4400,27 +4417,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4435,19 +4447,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134232494</v>
+        <v>133925272</v>
       </c>
       <c r="B35" t="n">
         <v>99112</v>
@@ -4486,13 +4498,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499476</v>
+        <v>499669</v>
       </c>
       <c r="R35" t="n">
-        <v>6622065</v>
+        <v>6622001</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4519,9 +4531,19 @@
           <t>2026-05-26</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4553,7 +4575,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135059471</v>
+        <v>134232494</v>
       </c>
       <c r="B36" t="n">
         <v>99112</v>
@@ -4586,29 +4608,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499368</v>
+        <v>499476</v>
       </c>
       <c r="R36" t="n">
-        <v>6621511</v>
+        <v>6622065</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4632,22 +4644,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>09:58</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>09:58</t>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4662,19 +4669,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135060107</v>
+        <v>135059471</v>
       </c>
       <c r="B37" t="n">
         <v>99112</v>
@@ -4704,7 +4711,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4723,10 +4730,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499479</v>
+        <v>499368</v>
       </c>
       <c r="R37" t="n">
-        <v>6621502</v>
+        <v>6621511</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4758,7 +4765,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4768,7 +4775,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4795,7 +4802,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135060756</v>
+        <v>135060107</v>
       </c>
       <c r="B38" t="n">
         <v>99112</v>
@@ -4825,7 +4832,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4844,10 +4851,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499547</v>
+        <v>499479</v>
       </c>
       <c r="R38" t="n">
-        <v>6621511</v>
+        <v>6621502</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4879,7 +4886,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4889,7 +4896,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4916,7 +4923,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135061272</v>
+        <v>135060756</v>
       </c>
       <c r="B39" t="n">
         <v>99112</v>
@@ -4946,7 +4953,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4965,10 +4972,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499557</v>
+        <v>499547</v>
       </c>
       <c r="R39" t="n">
-        <v>6621707</v>
+        <v>6621511</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -5000,7 +5007,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5010,7 +5017,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5037,7 +5044,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135061286</v>
+        <v>135061272</v>
       </c>
       <c r="B40" t="n">
         <v>99112</v>
@@ -5067,7 +5074,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5086,10 +5093,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499553</v>
+        <v>499557</v>
       </c>
       <c r="R40" t="n">
-        <v>6621728</v>
+        <v>6621707</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5121,7 +5128,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5131,7 +5138,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5158,7 +5165,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135061473</v>
+        <v>135061286</v>
       </c>
       <c r="B41" t="n">
         <v>99112</v>
@@ -5188,30 +5195,32 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499542</v>
+        <v>499553</v>
       </c>
       <c r="R41" t="n">
-        <v>6621615</v>
+        <v>6621728</v>
       </c>
       <c r="S41" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5238,37 +5247,46 @@
           <t>2026-07-11</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anna Hammar</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135061528</v>
+        <v>135061473</v>
       </c>
       <c r="B42" t="n">
         <v>99112</v>
@@ -5298,32 +5316,30 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499602</v>
+        <v>499542</v>
       </c>
       <c r="R42" t="n">
-        <v>6621752</v>
+        <v>6621615</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5350,46 +5366,37 @@
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Anna Hammar</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135061587</v>
+        <v>135061528</v>
       </c>
       <c r="B43" t="n">
         <v>99112</v>
@@ -5419,7 +5426,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5438,10 +5445,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499604</v>
+        <v>499602</v>
       </c>
       <c r="R43" t="n">
-        <v>6621788</v>
+        <v>6621752</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5473,7 +5480,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5483,7 +5490,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5510,7 +5517,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135061709</v>
+        <v>135061587</v>
       </c>
       <c r="B44" t="n">
         <v>99112</v>
@@ -5540,7 +5547,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5559,10 +5566,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499581</v>
+        <v>499604</v>
       </c>
       <c r="R44" t="n">
-        <v>6621818</v>
+        <v>6621788</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5594,7 +5601,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5604,7 +5611,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5631,7 +5638,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135062653</v>
+        <v>135061709</v>
       </c>
       <c r="B45" t="n">
         <v>99112</v>
@@ -5661,7 +5668,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5676,14 +5683,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499548</v>
+        <v>499581</v>
       </c>
       <c r="R45" t="n">
-        <v>6622078</v>
+        <v>6621818</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5715,7 +5722,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5725,7 +5732,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5752,7 +5759,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135064670</v>
+        <v>135062653</v>
       </c>
       <c r="B46" t="n">
         <v>99112</v>
@@ -5782,7 +5789,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5801,10 +5808,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499511</v>
+        <v>499548</v>
       </c>
       <c r="R46" t="n">
-        <v>6622238</v>
+        <v>6622078</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5836,7 +5843,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5846,7 +5853,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5873,10 +5880,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135059208</v>
+        <v>135064670</v>
       </c>
       <c r="B47" t="n">
-        <v>99219</v>
+        <v>99112</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5884,21 +5891,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5913,19 +5920,19 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bastmossen, Bastmossen, Vstm</t>
+          <t>Svartbergstäppan, Svartbergstäppan, Vstm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499387</v>
+        <v>499511</v>
       </c>
       <c r="R47" t="n">
-        <v>6621650</v>
+        <v>6622238</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5957,7 +5964,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5967,7 +5974,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5994,10 +6001,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135061615</v>
+        <v>135138158</v>
       </c>
       <c r="B48" t="n">
-        <v>111153</v>
+        <v>99112</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6005,27 +6012,36 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220240</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6034,10 +6050,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499604</v>
+        <v>499412</v>
       </c>
       <c r="R48" t="n">
-        <v>6621787</v>
+        <v>6621454</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -6064,27 +6080,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6104,17 +6115,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135063768</v>
+        <v>135059208</v>
       </c>
       <c r="B49" t="n">
-        <v>98060</v>
+        <v>99219</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6122,34 +6133,48 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221945</v>
+        <v>219847</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499655</v>
+        <v>499387</v>
       </c>
       <c r="R49" t="n">
-        <v>6622288</v>
+        <v>6621650</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6181,7 +6206,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6191,7 +6216,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6211,17 +6236,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135063876</v>
+        <v>135061615</v>
       </c>
       <c r="B50" t="n">
-        <v>99472</v>
+        <v>111153</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6229,16 +6254,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222812</v>
+        <v>220240</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6247,16 +6272,21 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Bastmossen, Bastmossen, Vstm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499672</v>
+        <v>499604</v>
       </c>
       <c r="R50" t="n">
-        <v>6622314</v>
+        <v>6621787</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6288,7 +6318,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6298,7 +6328,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6325,10 +6360,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134232497</v>
+        <v>135063768</v>
       </c>
       <c r="B51" t="n">
-        <v>80438</v>
+        <v>98060</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6336,41 +6371,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499572</v>
+        <v>499655</v>
       </c>
       <c r="R51" t="n">
-        <v>6622131</v>
+        <v>6622288</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6394,17 +6425,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6419,22 +6455,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135063104</v>
+        <v>135063876</v>
       </c>
       <c r="B52" t="n">
-        <v>80438</v>
+        <v>99472</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6442,21 +6478,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229497</v>
+        <v>222812</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6466,10 +6502,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499616</v>
+        <v>499672</v>
       </c>
       <c r="R52" t="n">
-        <v>6622213</v>
+        <v>6622314</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6501,7 +6537,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6511,12 +6547,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Vid basen av hänsynsasp.</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6543,7 +6574,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135063382</v>
+        <v>134232497</v>
       </c>
       <c r="B53" t="n">
         <v>80438</v>
@@ -6571,20 +6602,24 @@
           <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Södra Hagen, Södra Hagen, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499630</v>
+        <v>499572</v>
       </c>
       <c r="R53" t="n">
-        <v>6622258</v>
+        <v>6622131</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6608,27 +6643,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Basen på grav asp, ej hänsynssnitslad.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6643,15 +6668,239 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135063104</v>
+      </c>
+      <c r="B54" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>499616</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6622213</v>
+      </c>
+      <c r="S54" t="n">
+        <v>20</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Vid basen av hänsynsasp.</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
           <t>Therese Steiner</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
+      <c r="AX54" t="inlineStr">
         <is>
           <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
-      <c r="AY53" t="inlineStr"/>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135063382</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Södra Hagen, Södra Hagen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>499630</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6622258</v>
+      </c>
+      <c r="S55" t="n">
+        <v>20</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Basen på grav asp, ej hänsynssnitslad.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Therese Steiner, Anna Hammar</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -6236,7 +6236,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -4452,7 +4452,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -4452,7 +4452,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -3362,7 +3362,7 @@
         <v>499579</v>
       </c>
       <c r="R25" t="n">
-        <v>6622251</v>
+        <v>6622252</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3942,7 +3942,7 @@
         <v>499579</v>
       </c>
       <c r="R30" t="n">
-        <v>6622251</v>
+        <v>6622252</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -1804,7 +1804,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -3362,7 +3362,7 @@
         <v>499579</v>
       </c>
       <c r="R25" t="n">
-        <v>6622252</v>
+        <v>6622251</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3942,7 +3942,7 @@
         <v>499579</v>
       </c>
       <c r="R30" t="n">
-        <v>6622252</v>
+        <v>6622251</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>

--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -1804,7 +1804,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -2862,7 +2862,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3362,7 +3362,7 @@
         <v>499579</v>
       </c>
       <c r="R25" t="n">
-        <v>6622251</v>
+        <v>6622252</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3942,7 +3942,7 @@
         <v>499579</v>
       </c>
       <c r="R30" t="n">
-        <v>6622251</v>
+        <v>6622252</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -909,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -909,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -3362,7 +3362,7 @@
         <v>499579</v>
       </c>
       <c r="R25" t="n">
-        <v>6622252</v>
+        <v>6622251</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3942,7 +3942,7 @@
         <v>499579</v>
       </c>
       <c r="R30" t="n">
-        <v>6622252</v>
+        <v>6622251</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>

--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -3362,7 +3362,7 @@
         <v>499579</v>
       </c>
       <c r="R25" t="n">
-        <v>6622251</v>
+        <v>6622252</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3942,7 +3942,7 @@
         <v>499579</v>
       </c>
       <c r="R30" t="n">
-        <v>6622251</v>
+        <v>6622252</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>

--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -909,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -909,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -801,6 +806,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135063650</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -913,6 +923,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135059885</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135060163</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135060941</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1233,6 +1258,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135063711</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1350,6 +1380,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135060050</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1467,6 +1502,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135060358</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1579,6 +1619,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135064630</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1691,6 +1736,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135064766</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1804,10 +1854,15 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135061441</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1920,6 +1975,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135059028</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2032,6 +2092,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135059664</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2149,6 +2214,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135061981</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2261,6 +2331,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135062004</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2392,6 +2467,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135062059</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2509,6 +2589,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135062640</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2626,6 +2711,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135064589</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2754,6 +2844,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135143988</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2866,6 +2961,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135060672</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2978,6 +3078,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135060532</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3084,6 +3189,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232496</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3200,6 +3310,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135061152</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3316,6 +3431,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135063205</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3362,7 +3482,7 @@
         <v>499579</v>
       </c>
       <c r="R25" t="n">
-        <v>6622252</v>
+        <v>6622251</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3428,6 +3548,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135064184</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3544,6 +3669,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135059398</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3660,6 +3790,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135063052</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3776,6 +3911,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135063221</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3892,6 +4032,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135063830</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3942,7 +4087,7 @@
         <v>499579</v>
       </c>
       <c r="R30" t="n">
-        <v>6622252</v>
+        <v>6622251</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -4008,6 +4153,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135064196</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4120,6 +4270,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135060640</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4232,6 +4387,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135059764</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4344,6 +4504,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135059416</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4456,6 +4621,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135062618</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4572,6 +4742,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133925272</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4678,6 +4853,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232494</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4799,6 +4979,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135059471</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4920,6 +5105,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135060107</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5041,6 +5231,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135060756</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5162,6 +5357,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135061272</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5283,6 +5483,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135061286</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5393,6 +5598,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135061473</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5514,6 +5724,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135061528</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5635,6 +5850,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135061587</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5756,6 +5976,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135061709</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5877,6 +6102,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135062653</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5998,6 +6228,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135064670</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6119,6 +6354,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135138158</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6240,6 +6480,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135059208</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6357,6 +6602,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135061615</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6464,6 +6714,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135063768</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6571,6 +6826,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135063876</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6677,6 +6937,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232497</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6789,6 +7054,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135063104</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6901,8 +7171,69 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135063382</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -3482,7 +3482,7 @@
         <v>499579</v>
       </c>
       <c r="R25" t="n">
-        <v>6622251</v>
+        <v>6622252</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -4087,7 +4087,7 @@
         <v>499579</v>
       </c>
       <c r="R30" t="n">
-        <v>6622251</v>
+        <v>6622252</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>

--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135063650</v>
       </c>
       <c r="B2" t="n">
-        <v>96629</v>
+        <v>96673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>135059885</v>
       </c>
       <c r="B3" t="n">
-        <v>92370</v>
+        <v>92412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>135060163</v>
       </c>
       <c r="B4" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>135060941</v>
       </c>
       <c r="B5" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>135063711</v>
       </c>
       <c r="B6" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>135060050</v>
       </c>
       <c r="B7" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>135060358</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>135064630</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>135064766</v>
       </c>
       <c r="B10" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>135061441</v>
       </c>
       <c r="B11" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>135059028</v>
       </c>
       <c r="B12" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>135059664</v>
       </c>
       <c r="B13" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>135061981</v>
       </c>
       <c r="B14" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>135062004</v>
       </c>
       <c r="B15" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>135062059</v>
       </c>
       <c r="B16" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135062640</v>
       </c>
       <c r="B17" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>135064589</v>
       </c>
       <c r="B18" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>135143988</v>
       </c>
       <c r="B19" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>135061152</v>
       </c>
       <c r="B23" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>135063205</v>
       </c>
       <c r="B24" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>135064184</v>
       </c>
       <c r="B25" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3559,7 +3559,7 @@
         <v>135059398</v>
       </c>
       <c r="B26" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>135063052</v>
       </c>
       <c r="B27" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>135063221</v>
       </c>
       <c r="B28" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>135063830</v>
       </c>
       <c r="B29" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135064196</v>
       </c>
       <c r="B30" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4281,7 +4281,7 @@
         <v>135059764</v>
       </c>
       <c r="B32" t="n">
-        <v>8449</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>135059416</v>
       </c>
       <c r="B33" t="n">
-        <v>56706</v>
+        <v>56711</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>135062618</v>
       </c>
       <c r="B34" t="n">
-        <v>56706</v>
+        <v>56711</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>135059471</v>
       </c>
       <c r="B37" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>135060107</v>
       </c>
       <c r="B38" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>135060756</v>
       </c>
       <c r="B39" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>135061272</v>
       </c>
       <c r="B40" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>135061286</v>
       </c>
       <c r="B41" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>135061473</v>
       </c>
       <c r="B42" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>135061528</v>
       </c>
       <c r="B43" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>135061587</v>
       </c>
       <c r="B44" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>135061709</v>
       </c>
       <c r="B45" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>135062653</v>
       </c>
       <c r="B46" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         <v>135064670</v>
       </c>
       <c r="B47" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>135138158</v>
       </c>
       <c r="B48" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>135059208</v>
       </c>
       <c r="B49" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>135061615</v>
       </c>
       <c r="B50" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>135063768</v>
       </c>
       <c r="B51" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>135063876</v>
       </c>
       <c r="B52" t="n">
-        <v>99472</v>
+        <v>99519</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>135063104</v>
       </c>
       <c r="B54" t="n">
-        <v>80438</v>
+        <v>80476</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>135063382</v>
       </c>
       <c r="B55" t="n">
-        <v>80438</v>
+        <v>80476</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135063650</v>
       </c>
       <c r="B2" t="n">
-        <v>96673</v>
+        <v>96700</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>135059885</v>
       </c>
       <c r="B3" t="n">
-        <v>92412</v>
+        <v>92439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>135060163</v>
       </c>
       <c r="B4" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>135060941</v>
       </c>
       <c r="B5" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>135063711</v>
       </c>
       <c r="B6" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>135059471</v>
       </c>
       <c r="B37" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>135060107</v>
       </c>
       <c r="B38" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>135060756</v>
       </c>
       <c r="B39" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>135061272</v>
       </c>
       <c r="B40" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>135061286</v>
       </c>
       <c r="B41" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>135061473</v>
       </c>
       <c r="B42" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>135061528</v>
       </c>
       <c r="B43" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>135061587</v>
       </c>
       <c r="B44" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>135061709</v>
       </c>
       <c r="B45" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>135062653</v>
       </c>
       <c r="B46" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         <v>135064670</v>
       </c>
       <c r="B47" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>135138158</v>
       </c>
       <c r="B48" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>135059208</v>
       </c>
       <c r="B49" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>135061615</v>
       </c>
       <c r="B50" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>135063768</v>
       </c>
       <c r="B51" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>135063876</v>
       </c>
       <c r="B52" t="n">
-        <v>99519</v>
+        <v>99546</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>135063104</v>
       </c>
       <c r="B54" t="n">
-        <v>80476</v>
+        <v>80503</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>135063382</v>
       </c>
       <c r="B55" t="n">
-        <v>80476</v>
+        <v>80503</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 25097-2026 artfynd.xlsx
+++ b/artfynd/A 25097-2026 artfynd.xlsx
@@ -3544,7 +3544,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
